--- a/projects/unified-order-management-catering/08_Backlog_RICE_RTM.xlsx
+++ b/projects/unified-order-management-catering/08_Backlog_RICE_RTM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Админ\Desktop\Бизнес-системная аналитика\Системная аналитика\Кейтеринг\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Админ\Desktop\Бизнес-системная аналитика\Git\business-analytics-portfolio\projects\unified-order-management-catering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5C887E-63FF-482C-8068-C75DD5B6C19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E30DE11-36C8-48E2-9C37-233347E5C97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="120" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17430" yWindow="5640" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog" sheetId="1" r:id="rId1"/>
@@ -62,9 +62,6 @@
     <t>Must</t>
   </si>
   <si>
-    <t>Готов к разработке</t>
-  </si>
-  <si>
     <t>Версия документа: v.1.2</t>
   </si>
   <si>
@@ -116,9 +113,6 @@
     <t>Как Клиент Я хочу удалить товар из корзины</t>
   </si>
   <si>
-    <t>Как Клиент Я хочу оформить и оплатить заказ и получить подтверждение</t>
-  </si>
-  <si>
     <t>Как Клиент Я хочу видеть только доступные даты при оформлении заказа</t>
   </si>
   <si>
@@ -144,9 +138,6 @@
   </si>
   <si>
     <t>На доработке</t>
-  </si>
-  <si>
-    <t>Надёжность, аналитика и UX (Full)</t>
   </si>
   <si>
     <t>Работа менеджера с заказами</t>
@@ -321,21 +312,6 @@
   </si>
   <si>
     <r>
-      <t>Impact</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> — насколько сильно повлияет на ключевую метрику (условная шкала, напр.: 3 = massive, 1 = high, 0.5 = medium, 0.25 = low).</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>Confidence</t>
     </r>
     <r>
@@ -389,9 +365,6 @@
     <t>UC-01</t>
   </si>
   <si>
-    <t>UC-02</t>
-  </si>
-  <si>
     <t>FR-01</t>
   </si>
   <si>
@@ -453,6 +426,33 @@
   </si>
   <si>
     <t>FR-09</t>
+  </si>
+  <si>
+    <t>Как Клиент Я хочу оформить, оплатить заказ и получить подтверждение</t>
+  </si>
+  <si>
+    <t>Could</t>
+  </si>
+  <si>
+    <t>Новый сайт, надёжность, аналитика и UX (Full)</t>
+  </si>
+  <si>
+    <r>
+      <t>Impact</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — насколько сильно повлияет на ключевую метрику</t>
+    </r>
+  </si>
+  <si>
+    <t>UC-04, UC-2</t>
   </si>
 </sst>
 </file>
@@ -462,12 +462,28 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -527,7 +543,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -587,31 +603,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -638,45 +663,106 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -958,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.85546875" customWidth="1"/>
@@ -967,36 +1053,36 @@
     <col min="6" max="6" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
@@ -1010,269 +1096,281 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>11</v>
+    <row r="6" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="33" t="s">
+        <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="6">
         <f>RICE!P3</f>
-        <v>48.300000000000004</v>
+        <v>72</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>33</v>
+      </c>
+      <c r="H6" s="32"/>
+    </row>
+    <row r="7" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="33" t="s">
+        <v>11</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="6">
-        <f>RICE!P4</f>
-        <v>48.300000000000004</v>
+        <f>RICE!P5</f>
+        <v>14</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>13</v>
+        <v>33</v>
+      </c>
+      <c r="H7" s="32"/>
+    </row>
+    <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="33" t="s">
+        <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="6">
-        <f>RICE!P5</f>
-        <v>50.4</v>
+        <f>RICE!P6</f>
+        <v>14</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>14</v>
+        <v>33</v>
+      </c>
+      <c r="H8" s="32"/>
+    </row>
+    <row r="9" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="33" t="s">
+        <v>13</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="6">
-        <f>RICE!P6</f>
-        <v>63</v>
+        <f>RICE!P7</f>
+        <v>14</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>33</v>
+      </c>
+      <c r="H9" s="32"/>
+    </row>
+    <row r="10" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>14</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="6">
-        <f>RICE!P7</f>
-        <v>72</v>
+        <f>RICE!P8</f>
+        <v>28</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>33</v>
+      </c>
+      <c r="G10" s="31"/>
+      <c r="H10" s="32"/>
+    </row>
+    <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="33" t="s">
+        <v>15</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>28</v>
+      <c r="C11" s="20" t="s">
+        <v>112</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="6">
+        <f>RICE!P4</f>
+        <v>72</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="47">
         <f>RICE!P9</f>
-        <v>14</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="31"/>
+      <c r="H12" s="32"/>
+    </row>
+    <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="6">
+      <c r="B13" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="47">
         <f>RICE!P10</f>
-        <v>14</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+        <v>17.5</v>
+      </c>
+      <c r="F13" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="32"/>
+    </row>
+    <row r="14" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="B14" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="47">
+        <f>RICE!P11</f>
+        <v>10.5</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="31"/>
+      <c r="H14" s="32"/>
+    </row>
+    <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="47">
+        <f>RICE!P12</f>
+        <v>21</v>
+      </c>
+      <c r="F15" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="32"/>
+    </row>
+    <row r="16" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="6">
-        <f>RICE!P11</f>
-        <v>14</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="6">
-        <f>RICE!P12</f>
-        <v>28</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="6">
-        <f>RICE!P8</f>
-        <v>72</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="E16" s="6">
         <f>RICE!P13</f>
         <v>20</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>120</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>119</v>
       </c>
       <c r="E17" s="6">
         <f>RICE!P14</f>
         <v>0.4</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -1301,444 +1399,444 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="C1" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="22" t="s">
+      <c r="B1" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="25"/>
+    </row>
+    <row r="2" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="24"/>
-    </row>
-    <row r="2" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="M2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="26">
         <v>80</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="G3" s="26">
+        <f>(F3+H3)/2</f>
+        <v>100</v>
+      </c>
+      <c r="H3" s="26">
+        <v>120</v>
+      </c>
+      <c r="I3" s="28">
+        <f>(F3+4*G3+H3)/6</f>
+        <v>100</v>
+      </c>
+      <c r="J3" s="26">
+        <v>300</v>
+      </c>
+      <c r="K3" s="26">
+        <v>2</v>
+      </c>
+      <c r="L3" s="26">
+        <v>0.6</v>
+      </c>
+      <c r="M3" s="26">
+        <f>I3/40</f>
+        <v>2.5</v>
+      </c>
+      <c r="N3" s="27">
+        <f>J3*K3*L3/M3</f>
+        <v>144</v>
+      </c>
+      <c r="O3" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="P3" s="17">
+        <f>N$3*O3</f>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="28"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="P4" s="17">
+        <f>N$3*O4</f>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="25">
-        <v>80</v>
-      </c>
-      <c r="G3" s="25">
-        <f>(F3+H3)/2</f>
-        <v>120</v>
-      </c>
-      <c r="H3" s="25">
-        <v>160</v>
-      </c>
-      <c r="I3" s="27">
-        <f>(F3+4*G3+H3)/6</f>
-        <v>120</v>
-      </c>
-      <c r="J3" s="25">
-        <v>300</v>
-      </c>
-      <c r="K3" s="25">
-        <v>3</v>
-      </c>
-      <c r="L3" s="25">
-        <v>0.7</v>
-      </c>
-      <c r="M3" s="25">
-        <f>I3/8/5</f>
-        <v>3</v>
-      </c>
-      <c r="N3" s="26">
-        <f>J3*K3*L3/M3</f>
-        <v>210</v>
-      </c>
-      <c r="O3" s="14">
-        <v>0.23</v>
-      </c>
-      <c r="P3" s="16">
-        <f>N$3*O3</f>
-        <v>48.300000000000004</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="27"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="14">
-        <v>0.23</v>
-      </c>
-      <c r="P4" s="16">
-        <f t="shared" ref="P4:P6" si="0">N$3*O4</f>
-        <v>48.300000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="27"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="26"/>
+      <c r="E5" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="26">
+        <v>80</v>
+      </c>
+      <c r="G5" s="26">
+        <f>(F5+H5)/2</f>
+        <v>120</v>
+      </c>
+      <c r="H5" s="26">
+        <v>160</v>
+      </c>
+      <c r="I5" s="28">
+        <f>(F5+4*G5+H5)/6</f>
+        <v>120</v>
+      </c>
+      <c r="J5" s="26">
+        <v>100</v>
+      </c>
+      <c r="K5" s="26">
+        <v>3</v>
+      </c>
+      <c r="L5" s="26">
+        <v>0.7</v>
+      </c>
+      <c r="M5" s="26">
+        <f>I5/40</f>
+        <v>3</v>
+      </c>
+      <c r="N5" s="27">
+        <f>J5*K5*L5/M5</f>
+        <v>70</v>
+      </c>
       <c r="O5" s="14">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="P5" s="16">
-        <f t="shared" si="0"/>
-        <v>50.4</v>
+        <f>N$5*O5</f>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="27"/>
-      <c r="B6" s="28"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="29"/>
       <c r="C6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="P6" s="16">
+        <f t="shared" ref="P6:P8" si="0">N$5*O6</f>
         <v>14</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="P6" s="16">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>41</v>
-      </c>
+    </row>
+    <row r="7" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="28"/>
+      <c r="B7" s="29"/>
       <c r="C7" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="25">
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="P7" s="16">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="28"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="14">
+        <v>0.4</v>
+      </c>
+      <c r="P8" s="16">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="43" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="39">
         <v>80</v>
       </c>
-      <c r="G7" s="25">
-        <f>(F7+H7)/2</f>
-        <v>100</v>
-      </c>
-      <c r="H7" s="25">
-        <v>120</v>
-      </c>
-      <c r="I7" s="27">
-        <f>(F7+4*G7+H7)/6</f>
-        <v>100</v>
-      </c>
-      <c r="J7" s="25">
-        <v>300</v>
-      </c>
-      <c r="K7" s="25">
-        <v>2</v>
-      </c>
-      <c r="L7" s="25">
-        <v>0.6</v>
-      </c>
-      <c r="M7" s="25">
-        <f>I7/40</f>
-        <v>2.5</v>
-      </c>
-      <c r="N7" s="26">
-        <f>J7*K7*L7/M7</f>
-        <v>144</v>
-      </c>
-      <c r="O7" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="P7" s="17">
-        <f>N$7*O7</f>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="27"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="P8" s="17">
-        <f>N$7*O8</f>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="25">
-        <v>80</v>
-      </c>
-      <c r="G9" s="25">
+      <c r="G9" s="39">
         <f>(F9+H9)/2</f>
         <v>120</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="39">
         <v>160</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="35">
         <f>(F9+4*G9+H9)/6</f>
         <v>120</v>
       </c>
-      <c r="J9" s="25">
-        <v>100</v>
-      </c>
-      <c r="K9" s="25">
+      <c r="J9" s="39">
+        <v>300</v>
+      </c>
+      <c r="K9" s="39">
+        <v>1</v>
+      </c>
+      <c r="L9" s="39">
+        <v>0.7</v>
+      </c>
+      <c r="M9" s="39">
+        <f>I9/8/5</f>
         <v>3</v>
       </c>
-      <c r="L9" s="25">
-        <v>0.7</v>
-      </c>
-      <c r="M9" s="25">
-        <f>I9/40</f>
-        <v>3</v>
-      </c>
-      <c r="N9" s="26">
+      <c r="N9" s="40">
         <f>J9*K9*L9/M9</f>
         <v>70</v>
       </c>
-      <c r="O9" s="14">
-        <v>0.2</v>
-      </c>
-      <c r="P9" s="16">
+      <c r="O9" s="41">
+        <v>0.3</v>
+      </c>
+      <c r="P9" s="42">
         <f>N$9*O9</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="43" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="35"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="14">
-        <v>0.2</v>
-      </c>
-      <c r="P10" s="16">
-        <f t="shared" ref="P10:P12" si="1">N$9*O10</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="3" t="s">
+      <c r="D10" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="41">
+        <v>0.25</v>
+      </c>
+      <c r="P10" s="42">
+        <f>N$9*O10</f>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="43" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="35"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="14">
-        <v>0.2</v>
-      </c>
-      <c r="P11" s="16">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="3" t="s">
+      <c r="D11" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="41">
+        <v>0.15</v>
+      </c>
+      <c r="P11" s="42">
+        <f>N$9*O11</f>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="43" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="35"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="14">
-        <v>0.4</v>
-      </c>
-      <c r="P12" s="16">
-        <f t="shared" si="1"/>
-        <v>28</v>
+      <c r="D12" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="41">
+        <v>0.3</v>
+      </c>
+      <c r="P12" s="42">
+        <f>N$9*O12</f>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F13" s="12">
         <v>80</v>
@@ -1781,19 +1879,19 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F14" s="12">
         <v>160</v>
@@ -1836,10 +1934,10 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17"/>
@@ -1852,7 +1950,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1866,10 +1964,10 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="F19" s="18"/>
       <c r="G19"/>
@@ -1895,11 +1993,11 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B21" s="11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C21" s="11"/>
       <c r="E21" s="18" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F21" s="18"/>
       <c r="G21"/>
@@ -1912,10 +2010,10 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B22" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
@@ -1929,13 +2027,13 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B23" s="11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F23" s="18"/>
       <c r="G23"/>
@@ -1948,75 +2046,75 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B24" s="11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B25" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="E5:E8"/>
     <mergeCell ref="C1:D2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="E1:I1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="E3:E6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="I9:I12"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="I5:I8"/>
     <mergeCell ref="F9:F12"/>
     <mergeCell ref="G9:G12"/>
     <mergeCell ref="H9:H12"/>
-    <mergeCell ref="I3:I6"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I12"/>
-    <mergeCell ref="F3:F6"/>
-    <mergeCell ref="G3:G6"/>
-    <mergeCell ref="H3:H6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="K5:K8"/>
+    <mergeCell ref="L5:L8"/>
+    <mergeCell ref="M5:M8"/>
+    <mergeCell ref="N5:N8"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
     <mergeCell ref="J9:J12"/>
     <mergeCell ref="K9:K12"/>
     <mergeCell ref="L9:L12"/>
     <mergeCell ref="M9:M12"/>
     <mergeCell ref="N9:N12"/>
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="K3:K6"/>
-    <mergeCell ref="L3:L6"/>
-    <mergeCell ref="M3:M6"/>
-    <mergeCell ref="N3:N6"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -2036,240 +2134,240 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
+      <c r="A1" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="E2" s="19" t="s">
+      <c r="D3" s="19" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>103</v>
-      </c>
       <c r="E3" s="19" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="19" t="s">
+      <c r="B7" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="19" t="s">
+    </row>
+    <row r="9" spans="1:5" s="50" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E9" s="44" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="50" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="44" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="19" t="s">
+      <c r="D10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="E8" s="19" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" s="19" t="s">
+    </row>
+    <row r="11" spans="1:5" s="50" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="E9" s="19" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+    </row>
+    <row r="12" spans="1:5" s="50" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>105</v>
+      <c r="B12" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="44" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/projects/unified-order-management-catering/08_Backlog_RICE_RTM.xlsx
+++ b/projects/unified-order-management-catering/08_Backlog_RICE_RTM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Админ\Desktop\Бизнес-системная аналитика\Git\business-analytics-portfolio\projects\unified-order-management-catering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E30DE11-36C8-48E2-9C37-233347E5C97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8C7306-322E-4A48-B31C-4F507030F522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17430" yWindow="5640" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4215" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog" sheetId="1" r:id="rId1"/>
@@ -462,12 +462,20 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -616,153 +624,156 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1054,14 +1065,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1103,7 +1114,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="24" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -1122,10 +1133,10 @@
       <c r="F6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="32"/>
+      <c r="H6" s="23"/>
     </row>
     <row r="7" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="24" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1144,10 +1155,10 @@
       <c r="F7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="32"/>
+      <c r="H7" s="23"/>
     </row>
     <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="24" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -1166,10 +1177,10 @@
       <c r="F8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="32"/>
+      <c r="H8" s="23"/>
     </row>
     <row r="9" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="24" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1188,10 +1199,10 @@
       <c r="F9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="32"/>
+      <c r="H9" s="23"/>
     </row>
     <row r="10" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="24" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="5" t="s">
@@ -1210,11 +1221,11 @@
       <c r="F10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="23"/>
     </row>
     <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="24" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1235,100 +1246,100 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="34">
         <f>RICE!P9</f>
         <v>21</v>
       </c>
-      <c r="F12" s="45" t="s">
+      <c r="F12" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="31"/>
-      <c r="H12" s="32"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="23"/>
     </row>
     <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="47">
+      <c r="E13" s="34">
         <f>RICE!P10</f>
         <v>17.5</v>
       </c>
-      <c r="F13" s="45" t="s">
+      <c r="F13" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="23"/>
     </row>
     <row r="14" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="34">
         <f>RICE!P11</f>
         <v>10.5</v>
       </c>
-      <c r="F14" s="45" t="s">
+      <c r="F14" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="31"/>
-      <c r="H14" s="32"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="23"/>
     </row>
     <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="C15" s="49" t="s">
+      <c r="C15" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="47">
+      <c r="E15" s="34">
         <f>RICE!P12</f>
         <v>21</v>
       </c>
-      <c r="F15" s="45" t="s">
+      <c r="F15" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="32"/>
+      <c r="H15" s="23"/>
     </row>
     <row r="16" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A16" s="33" t="s">
+      <c r="A16" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="25" t="s">
         <v>120</v>
       </c>
       <c r="C16" s="5" t="s">
@@ -1346,10 +1357,10 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="51" t="s">
         <v>120</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -1370,7 +1381,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -1399,38 +1410,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28" t="s">
+      <c r="D1" s="39"/>
+      <c r="E1" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="23" t="s">
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="25"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="48"/>
     </row>
     <row r="2" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="A2" s="39"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
       <c r="E2" s="3" t="s">
         <v>46</v>
       </c>
@@ -1469,10 +1480,10 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="40" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -1481,37 +1492,37 @@
       <c r="D3" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="41">
         <v>80</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="41">
         <f>(F3+H3)/2</f>
         <v>100</v>
       </c>
-      <c r="H3" s="26">
+      <c r="H3" s="41">
         <v>120</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="39">
         <f>(F3+4*G3+H3)/6</f>
         <v>100</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="41">
         <v>300</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="41">
         <v>2</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="41">
         <v>0.6</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="41">
         <f>I3/40</f>
         <v>2.5</v>
       </c>
-      <c r="N3" s="27">
+      <c r="N3" s="45">
         <f>J3*K3*L3/M3</f>
         <v>144</v>
       </c>
@@ -1524,24 +1535,24 @@
       </c>
     </row>
     <row r="4" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="29"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
       <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="27"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="45"/>
       <c r="O4" s="14">
         <v>0.5</v>
       </c>
@@ -1551,10 +1562,10 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="40" t="s">
         <v>34</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1563,37 +1574,37 @@
       <c r="D5" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="41">
         <v>80</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="41">
         <f>(F5+H5)/2</f>
         <v>120</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="41">
         <v>160</v>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="39">
         <f>(F5+4*G5+H5)/6</f>
         <v>120</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="41">
         <v>100</v>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="41">
         <v>3</v>
       </c>
-      <c r="L5" s="26">
+      <c r="L5" s="41">
         <v>0.7</v>
       </c>
-      <c r="M5" s="26">
+      <c r="M5" s="41">
         <f>I5/40</f>
         <v>3</v>
       </c>
-      <c r="N5" s="27">
+      <c r="N5" s="45">
         <f>J5*K5*L5/M5</f>
         <v>70</v>
       </c>
@@ -1606,24 +1617,24 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
-      <c r="B6" s="29"/>
+      <c r="A6" s="39"/>
+      <c r="B6" s="40"/>
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="27"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="45"/>
       <c r="O6" s="14">
         <v>0.2</v>
       </c>
@@ -1633,24 +1644,24 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="27"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="45"/>
       <c r="O7" s="14">
         <v>0.2</v>
       </c>
@@ -1660,24 +1671,24 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29"/>
+      <c r="A8" s="39"/>
+      <c r="B8" s="40"/>
       <c r="C8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="27"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="45"/>
       <c r="O8" s="14">
         <v>0.4</v>
       </c>
@@ -1686,138 +1697,138 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="43" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
+    <row r="9" spans="1:16" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="44">
         <v>80</v>
       </c>
-      <c r="G9" s="39">
+      <c r="G9" s="44">
         <f>(F9+H9)/2</f>
         <v>120</v>
       </c>
-      <c r="H9" s="39">
+      <c r="H9" s="44">
         <v>160</v>
       </c>
-      <c r="I9" s="35">
+      <c r="I9" s="43">
         <f>(F9+4*G9+H9)/6</f>
         <v>120</v>
       </c>
-      <c r="J9" s="39">
+      <c r="J9" s="44">
         <v>300</v>
       </c>
-      <c r="K9" s="39">
+      <c r="K9" s="44">
         <v>1</v>
       </c>
-      <c r="L9" s="39">
+      <c r="L9" s="44">
         <v>0.7</v>
       </c>
-      <c r="M9" s="39">
+      <c r="M9" s="44">
         <f>I9/8/5</f>
         <v>3</v>
       </c>
-      <c r="N9" s="40">
+      <c r="N9" s="49">
         <f>J9*K9*L9/M9</f>
         <v>70</v>
       </c>
-      <c r="O9" s="41">
+      <c r="O9" s="28">
         <v>0.3</v>
       </c>
-      <c r="P9" s="42">
+      <c r="P9" s="29">
         <f>N$9*O9</f>
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="43" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="35"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="37" t="s">
+    <row r="10" spans="1:16" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="43"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="41">
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="28">
         <v>0.25</v>
       </c>
-      <c r="P10" s="42">
+      <c r="P10" s="29">
         <f>N$9*O10</f>
         <v>17.5</v>
       </c>
     </row>
-    <row r="11" spans="1:16" s="43" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="37" t="s">
+    <row r="11" spans="1:16" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="43"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="41">
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="49"/>
+      <c r="O11" s="28">
         <v>0.15</v>
       </c>
-      <c r="P11" s="42">
+      <c r="P11" s="29">
         <f>N$9*O11</f>
         <v>10.5</v>
       </c>
     </row>
-    <row r="12" spans="1:16" s="43" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="35"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="37" t="s">
+    <row r="12" spans="1:16" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="43"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="41">
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="28">
         <v>0.3</v>
       </c>
-      <c r="P12" s="42">
+      <c r="P12" s="29">
         <f>N$9*O12</f>
         <v>21</v>
       </c>
@@ -2072,22 +2083,22 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="C1:D2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="E1:I1"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="E9:E12"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="J9:J12"/>
+    <mergeCell ref="K9:K12"/>
+    <mergeCell ref="L9:L12"/>
+    <mergeCell ref="M9:M12"/>
+    <mergeCell ref="N9:N12"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="K5:K8"/>
+    <mergeCell ref="L5:L8"/>
+    <mergeCell ref="M5:M8"/>
+    <mergeCell ref="N5:N8"/>
     <mergeCell ref="I9:I12"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="I5:I8"/>
@@ -2097,24 +2108,24 @@
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="K5:K8"/>
-    <mergeCell ref="L5:L8"/>
-    <mergeCell ref="M5:M8"/>
-    <mergeCell ref="N5:N8"/>
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="J9:J12"/>
-    <mergeCell ref="K9:K12"/>
-    <mergeCell ref="L9:L12"/>
-    <mergeCell ref="M9:M12"/>
-    <mergeCell ref="N9:N12"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="H5:H8"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -2134,13 +2145,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
@@ -2261,71 +2272,71 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="50" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
+    <row r="9" spans="1:5" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="44" t="s">
+      <c r="D9" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="31" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="50" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
+    <row r="10" spans="1:5" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="31" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="50" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
+    <row r="11" spans="1:5" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="31" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
+    <row r="12" spans="1:5" s="37" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="31" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2367,7 +2378,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/projects/unified-order-management-catering/08_Backlog_RICE_RTM.xlsx
+++ b/projects/unified-order-management-catering/08_Backlog_RICE_RTM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Админ\Desktop\Бизнес-системная аналитика\Git\business-analytics-portfolio\projects\unified-order-management-catering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8C7306-322E-4A48-B31C-4F507030F522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41551FC-83F7-499C-9D66-430CC7137A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4215" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4215" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="133">
   <si>
     <t>Product Backlog</t>
   </si>
@@ -452,7 +452,37 @@
     </r>
   </si>
   <si>
-    <t>UC-04, UC-2</t>
+    <t>BR</t>
+  </si>
+  <si>
+    <t>BR-01</t>
+  </si>
+  <si>
+    <t>BR-02</t>
+  </si>
+  <si>
+    <t>BR-03</t>
+  </si>
+  <si>
+    <t>BR-04</t>
+  </si>
+  <si>
+    <t>BR-05</t>
+  </si>
+  <si>
+    <t>BR-07</t>
+  </si>
+  <si>
+    <t>BR-08</t>
+  </si>
+  <si>
+    <t>BR-09</t>
+  </si>
+  <si>
+    <t>BR-10</t>
+  </si>
+  <si>
+    <t>UC-04, UC-02</t>
   </si>
 </sst>
 </file>
@@ -733,6 +763,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -740,9 +773,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -754,6 +784,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -771,9 +804,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1065,14 +1095,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1360,7 +1390,7 @@
       <c r="A17" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="38" t="s">
         <v>120</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -1410,38 +1440,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39" t="s">
+      <c r="D1" s="40"/>
+      <c r="E1" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="46" t="s">
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="49"/>
     </row>
     <row r="2" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
+      <c r="A2" s="40"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
       <c r="E2" s="3" t="s">
         <v>46</v>
       </c>
@@ -1480,10 +1510,10 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="45" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -1505,7 +1535,7 @@
       <c r="H3" s="41">
         <v>120</v>
       </c>
-      <c r="I3" s="39">
+      <c r="I3" s="40">
         <f>(F3+4*G3+H3)/6</f>
         <v>100</v>
       </c>
@@ -1522,7 +1552,7 @@
         <f>I3/40</f>
         <v>2.5</v>
       </c>
-      <c r="N3" s="45">
+      <c r="N3" s="46">
         <f>J3*K3*L3/M3</f>
         <v>144</v>
       </c>
@@ -1535,8 +1565,8 @@
       </c>
     </row>
     <row r="4" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="45"/>
       <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
@@ -1547,12 +1577,12 @@
       <c r="F4" s="41"/>
       <c r="G4" s="41"/>
       <c r="H4" s="41"/>
-      <c r="I4" s="39"/>
+      <c r="I4" s="40"/>
       <c r="J4" s="41"/>
       <c r="K4" s="41"/>
       <c r="L4" s="41"/>
       <c r="M4" s="41"/>
-      <c r="N4" s="45"/>
+      <c r="N4" s="46"/>
       <c r="O4" s="14">
         <v>0.5</v>
       </c>
@@ -1562,10 +1592,10 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="45" t="s">
         <v>34</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1587,7 +1617,7 @@
       <c r="H5" s="41">
         <v>160</v>
       </c>
-      <c r="I5" s="39">
+      <c r="I5" s="40">
         <f>(F5+4*G5+H5)/6</f>
         <v>120</v>
       </c>
@@ -1604,7 +1634,7 @@
         <f>I5/40</f>
         <v>3</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="46">
         <f>J5*K5*L5/M5</f>
         <v>70</v>
       </c>
@@ -1617,8 +1647,8 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="39"/>
-      <c r="B6" s="40"/>
+      <c r="A6" s="40"/>
+      <c r="B6" s="45"/>
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
@@ -1629,12 +1659,12 @@
       <c r="F6" s="41"/>
       <c r="G6" s="41"/>
       <c r="H6" s="41"/>
-      <c r="I6" s="39"/>
+      <c r="I6" s="40"/>
       <c r="J6" s="41"/>
       <c r="K6" s="41"/>
       <c r="L6" s="41"/>
       <c r="M6" s="41"/>
-      <c r="N6" s="45"/>
+      <c r="N6" s="46"/>
       <c r="O6" s="14">
         <v>0.2</v>
       </c>
@@ -1644,8 +1674,8 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="39"/>
-      <c r="B7" s="40"/>
+      <c r="A7" s="40"/>
+      <c r="B7" s="45"/>
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
@@ -1656,12 +1686,12 @@
       <c r="F7" s="41"/>
       <c r="G7" s="41"/>
       <c r="H7" s="41"/>
-      <c r="I7" s="39"/>
+      <c r="I7" s="40"/>
       <c r="J7" s="41"/>
       <c r="K7" s="41"/>
       <c r="L7" s="41"/>
       <c r="M7" s="41"/>
-      <c r="N7" s="45"/>
+      <c r="N7" s="46"/>
       <c r="O7" s="14">
         <v>0.2</v>
       </c>
@@ -1671,8 +1701,8 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="39"/>
-      <c r="B8" s="40"/>
+      <c r="A8" s="40"/>
+      <c r="B8" s="45"/>
       <c r="C8" s="3" t="s">
         <v>14</v>
       </c>
@@ -1683,12 +1713,12 @@
       <c r="F8" s="41"/>
       <c r="G8" s="41"/>
       <c r="H8" s="41"/>
-      <c r="I8" s="39"/>
+      <c r="I8" s="40"/>
       <c r="J8" s="41"/>
       <c r="K8" s="41"/>
       <c r="L8" s="41"/>
       <c r="M8" s="41"/>
-      <c r="N8" s="45"/>
+      <c r="N8" s="46"/>
       <c r="O8" s="14">
         <v>0.4</v>
       </c>
@@ -1740,7 +1770,7 @@
         <f>I9/8/5</f>
         <v>3</v>
       </c>
-      <c r="N9" s="49">
+      <c r="N9" s="50">
         <f>J9*K9*L9/M9</f>
         <v>70</v>
       </c>
@@ -1770,7 +1800,7 @@
       <c r="K10" s="44"/>
       <c r="L10" s="44"/>
       <c r="M10" s="44"/>
-      <c r="N10" s="49"/>
+      <c r="N10" s="50"/>
       <c r="O10" s="28">
         <v>0.25</v>
       </c>
@@ -1797,7 +1827,7 @@
       <c r="K11" s="44"/>
       <c r="L11" s="44"/>
       <c r="M11" s="44"/>
-      <c r="N11" s="49"/>
+      <c r="N11" s="50"/>
       <c r="O11" s="28">
         <v>0.15</v>
       </c>
@@ -1824,7 +1854,7 @@
       <c r="K12" s="44"/>
       <c r="L12" s="44"/>
       <c r="M12" s="44"/>
-      <c r="N12" s="49"/>
+      <c r="N12" s="50"/>
       <c r="O12" s="28">
         <v>0.3</v>
       </c>
@@ -2133,250 +2163,290 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F69C76F-3E70-4B8B-8B3B-F03AC502F466}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="8"/>
-    <col min="2" max="2" width="12.42578125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="8" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="2" width="9.140625" style="8"/>
+    <col min="3" max="3" width="12.42578125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="8" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>92</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="F2" s="19" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="D3" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="E3" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="F3" s="19" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>122</v>
-      </c>
       <c r="D4" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="F4" s="19" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>122</v>
-      </c>
       <c r="D5" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E5" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="F5" s="19" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>122</v>
-      </c>
       <c r="D6" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="F6" s="19" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>122</v>
-      </c>
       <c r="D7" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="F7" s="19" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="D8" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="E8" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="F8" s="19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="D9" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="E9" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="F9" s="31" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="31" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="D10" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="E10" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="F10" s="31" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="37" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="D11" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="E11" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="F11" s="31" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="31" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="D12" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="E12" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="F12" s="31" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="D13" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="E13" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="F13" s="19" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="D14" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="E14" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="F14" s="19" t="s">
         <v>113</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
